--- a/apps/web/public/importmallar/importmall-leverantorsadresser.xlsx
+++ b/apps/web/public/importmallar/importmall-leverantorsadresser.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -146,6 +146,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -157,12 +158,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1" style="4"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1" style="4"/>
     <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
@@ -236,88 +237,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leverantörsnummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Numret på en leverantör som redan finns i leverantörsregistret — importera leverantörerna först.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressnamn</t>
+          <t xml:space="preserve">Leverantörsnummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveransadressens benämning på leverantörskortet, max 100 tecken. Tom cell ger Leveransadress.</t>
+          <t xml:space="preserve">Numret på en leverantör som redan finns i leverantörsregistret — importera leverantörerna först.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lagret i Exempelstad</t>
+          <t xml:space="preserve">2001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressrad 1</t>
+          <t xml:space="preserve">Adressnamn</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -327,19 +313,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Första adressraden. Raderna 1–3 slås ihop till en adress med radbrytningar. En rad utan någon adressrad hoppas över, liksom en adress som är samma som leverantörens postadress eller en leveransadress som redan finns. Den första nya adressen blir leverantörens förvalda om leverantören saknar en och guidens Sätt som förvald leveransadress är ikryssad.</t>
+          <t xml:space="preserve">Leveransadressens benämning på leverantörskortet, max 100 tecken. Tom cell ger Leveransadress.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hamngatan 12</t>
+          <t xml:space="preserve">Lagret i Exempelstad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressrad 2</t>
+          <t xml:space="preserve">Adressrad 1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -349,19 +335,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andra adressraden, valfri — slås ihop med Adressrad 1.</t>
+          <t xml:space="preserve">Första adressraden. Raderna 1–3 slås ihop till en adress med radbrytningar. En rad utan någon adressrad hoppas över, liksom en adress som är samma som leverantörens postadress eller en leveransadress som redan finns. Den första nya adressen blir leverantörens förvalda om leverantören saknar en och guidens Sätt som förvald leveransadress är ikryssad.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godsmottagningen</t>
+          <t xml:space="preserve">Hamngatan 12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressrad 3</t>
+          <t xml:space="preserve">Adressrad 2</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -371,19 +357,19 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tredje adressraden, valfri — slås ihop med Adressrad 1.</t>
+          <t xml:space="preserve">Andra adressraden, valfri — slås ihop med Adressrad 1.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Port 2</t>
+          <t xml:space="preserve">Godsmottagningen</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postnummer</t>
+          <t xml:space="preserve">Adressrad 3</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -393,32 +379,54 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 20 tecken.</t>
+          <t xml:space="preserve">Tredje adressraden, valfri — slås ihop med Adressrad 1.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234 56</t>
+          <t xml:space="preserve">Port 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Postnummer</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Max 20 tecken.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234 56</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Stad</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Max 100 tecken.</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempelstad</t>
         </is>
